--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,104 +486,104 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb7f22df90a85481</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
+          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Computing Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=cd11c2a087aa2519</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University Bank</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ea5bb501a5ac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
@@ -898,11 +898,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766980d948b5a966</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31808d30684adc7</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b7c90a916e35d7</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597e12336f0812d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>employers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup(AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Taglynk</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2686471aa31f7398</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,182 +2411,182 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a195e515873c32</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - SQL (contract)</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a211a468bc1009b1</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hudson Oaks, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5102abee7a124d83</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2976,37 +2976,37 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,94 +3016,94 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer II - Onsite, Springfield, MO</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9462766e1bdc44b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Senior Java Engineer - Search Platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>Administration &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a374ae98e1a015fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c41c9642b0a2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Searchpros Staffing</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,155 +3531,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Searchpros Staffing</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43afc506f9234f19</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb7f22df90a85481</t>
+          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb7f22df90a85481</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Computing Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=cd11c2a087aa2519</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Computing Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd11c2a087aa2519</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,52 +1046,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Time Travel, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e75da89e25169</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd29cc3a867acb2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54788bf627331aec</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Senior Java Engineer - Search Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Administration &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Searchpros Staffing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,181 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Searchpros Staffing</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43afc506f9234f19</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb7f22df90a85481</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb7f22df90a85481</t>
+          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Senior Agentic AI Architect/Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=fd28b1ab1e76be27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior SIEM Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>ScaleHealthTech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,89 +2281,89 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=71b7a273236403b4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Sr. Data &amp; Integration Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Howard Hughes Holdings Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=63bb2c539c36b720</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>VerTALENTS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5421087114efdb9a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Software Engineer III - Full Stack Cloud (Java, React, AWS, GraphQL)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2ae0ecc8efc174</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Searchpros Staffing</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,15 +3356,575 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Backend Developer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer - Search Platform</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Visualization</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sr Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BECU</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2f84020e91f909f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ML Engineer / AI Operations</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Centric Consulting</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>The Wenger Group</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Lancaster, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Near-Miss Management</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Searchpros Staffing</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43afc506f9234f19</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23895720992f67e</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Computing Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd11c2a087aa2519</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>AWS Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Architect/Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd28b1ab1e76be27</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior SIEM Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>ScaleHealthTech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ScaleHealthTech</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Oracle, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,112 +2271,112 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b7a273236403b4</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integration Architect</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63bb2c539c36b720</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VerTALENTS</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5421087114efdb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Cloud (Java, React, AWS, GraphQL)</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2ae0ecc8efc174</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef60e87d626ac4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Intelligent Process Automation Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OSI Systems, Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Snoqualmie, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ce9084953b8335</t>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Analyst</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Near-Miss Management</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,402 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f84020e91f909f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Centric Consulting</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Intelligent Process Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>OSI Systems, Inc</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Snoqualmie, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>System Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>The Wenger Group</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Lancaster, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Near-Miss Management</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform (GCP) Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Searchpros Staffing</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43afc506f9234f19</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>SG360</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Wheeling, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ScaleHealthTech</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>ScaleHealthTech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e5ab137562f273</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Senior Software Engineer - PIMS2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
@@ -2393,25 +2393,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Intelligent Process Automation Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OSI Systems, Inc</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Snoqualmie, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, REST API integration, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks | Healthcare Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ScaleHealthTech</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28ed1d7de0513d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517d5c67d35acb4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PIMS2</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb3212fe9bc60d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,77 +2236,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RiseIT Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,122 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Near-Miss Management</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, PostgreSQL, ETL, GitHub Actions, Git, CloudWatch, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>SG360</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wheeling, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4568945a7df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SG360</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wheeling, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
+          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2171,29 +2171,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RiseIT Solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10f676b273ad2a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3400,41 +3400,6 @@
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Site Reliability Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, ECS, RDS, Hadoop, Hive, HBase</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddc68a9a0e8fb48</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,41 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -748,60 +748,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>SAP ERP Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cellentia Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=c25fb1848ca5bdb1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c895663eea835325</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc4b812b4def66e</t>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2171,29 +2171,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>SAP ERP Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cellentia Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=c25fb1848ca5bdb1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP ERP Senior Consultant</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cellentia Technologies</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25fb1848ca5bdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49b2a9c348862b</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac70edb0fb45c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2162,33 +2162,33 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,129 +2631,129 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer, Martech New</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3085,286 +3085,6 @@
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Solutions Engineer - Data Visualization</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,174 +766,174 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP ERP Senior Consultant</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cellentia Technologies</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25fb1848ca5bdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Python Fullstack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>SAP ERP Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Cellentia Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c25fb1848ca5bdb1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,137 +1091,137 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,182 +1991,182 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Legacy Food Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iowa City, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=38527d810c85ba5f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Data Engineer New</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer, Martech New</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Remote Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Software Engineer, Martech New</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,295 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Centric Consulting</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Visualization</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ML Engineer / AI Operations</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Backend Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Hadoop</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,122 +591,122 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Data Warehouse Developer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>NCCPA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12319e09a7649a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics / Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e51646c7f6b5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Checkr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,94 +1826,94 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>BAULI4-Computing Architect 4 - B78-Information/Data Architecture</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACL Digital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Kafka, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2ec8f7098e6405</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,33 +2092,33 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Legacy Food Group</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Iowa City, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38527d810c85ba5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer New</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c39b2953f289c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Power BI, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Cloud &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,172 +2561,172 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Senior System Engineer / Linux Server / Server Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Astreya Partners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer, Martech New</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Remote Sr. Data Engineer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, SQL Server, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8abfbc6f5545eda</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, Martech New</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HB Mechanical Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3085,286 +3085,6 @@
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Centric Consulting</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Solutions Engineer - Data Visualization</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Plainview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Data Platform Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>HB Mechanical Group</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP ERP Senior Consultant</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cellentia Technologies</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25fb1848ca5bdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,77 +1711,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BAULI4-Computing Architect 4 - B78-Information/Data Architecture</t>
+          <t>Data Engineer-Kiewit Nuclear Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ACL Digital</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Kafka, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2ec8f7098e6405</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,69 +1956,69 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,69 +2026,69 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Real Time Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,69 +2446,69 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00559f175e41fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior System Engineer / Linux Server / Server Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Astreya Partners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior System Engineer / Linux Server / Server Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Astreya Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer, Martech New</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HB Mechanical Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer, Martech New</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,42 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Fullstack Developer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Python Fullstack Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer II</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NCCPA</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Spark Streaming, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a3d4204cfe8c3</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe38a8a00ba491</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6786be8f8c217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions 1</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0dfe4a55ad8d320</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software DB Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Transaction Network Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Oracle, DynamoDB, ETL, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=27dddd28375427c7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62676487c6f8411a</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,77 +1711,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer-Kiewit Nuclear Solutions</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcc88e3afcff35d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,89 +1966,89 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Real Time Technologies</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9392a167ac0af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=be223724b244509d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=57b514b093e0ce21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,59 +2456,59 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior System Engineer / Linux Server / Server Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Astreya Partners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior System Engineer / Linux Server / Server Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Astreya Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HB Mechanical Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer, Martech New</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,76 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer, Martech New</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>The Knot Worldwide</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SG360</t>
+          <t>VaxCare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wheeling, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
+          <t>https://www.indeed.com/viewjob?jk=b7612e10491ad26f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>SG360</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wheeling, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6cf659d35d5289</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
@@ -671,42 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d9aeb0e7adc75</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Python Fullstack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Fullstack Developer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Checkr</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598ca45455673f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972d1a9bdec25467</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd935505fd26740e</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software DB Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Transaction Network Services</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Oracle, DynamoDB, ETL, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dddd28375427c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Sr. Software DB Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Transaction Network Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Oracle, DynamoDB, ETL, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=27dddd28375427c7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Informatica PowerCenter, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
@@ -1903,25 +1903,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Korean Bilingual Unix/Linux Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=f631ee05a50bf721</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computer Systems Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,94 +2001,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=65714e8b775bf6a7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95fab4dbabb261ff</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7529cd9eab44a3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLOps, CI/CD, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be223724b244509d</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b514b093e0ce21</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,172 +2421,172 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=be223724b244509d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=57b514b093e0ce21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior System Engineer / Linux Server / Server Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Astreya Partners</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Senior System Engineer / Linux Server / Server Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Astreya Partners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, Martech New</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,260 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Visualization</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Plainview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ML Engineer / AI Operations</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Platform Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HB Mechanical Group</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Backend Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer, Martech New</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>The Knot Worldwide</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069c52ba8f86fa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, PySpark, Scala, Time Travel, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Associate Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>VENERABLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Developer</t>
+          <t>Release Engineer/ DevOps engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VENERABLE</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc33f96a7d635cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Release Engineer/ DevOps engineer</t>
+          <t>Senior Software Engineer ll - Java - Web Search Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3efa9891a04eb92</t>
+          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ll - Java - Web Search Team</t>
+          <t>Python Fullstack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13715d715f12d9c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Fullstack Developer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Rincon Consultants</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Ventura, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Senior DevOps Engineer (Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AdvisorEngine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract)</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AdvisorEngine</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d325f0fea0c6b85d</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=50be6fdbd85cebea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer with OpenShift Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
+          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Sr. Software DB Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Transaction Network Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Oracle, DynamoDB, ETL, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=27dddd28375427c7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0520b2e91ff1af7</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software DB Development Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Transaction Network Services</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Oracle, DynamoDB, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dddd28375427c7</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>SOFTWARE DEVELOPER/ENGINEER</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>S.S. White Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOFTWARE DEVELOPER/ENGINEER</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S.S. White Technologies</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773b64ded556be00</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Korean Bilingual Unix Adminstrator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f631ee05a50bf721</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Korean Bilingual Unix/Linux Engineer</t>
+          <t>Distinguished Engineer, Cloud Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Hadoop, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631ee05a50bf721</t>
+          <t>https://www.indeed.com/viewjob?jk=84f499dac9552b99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Computer Systems Analyst</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65714e8b775bf6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Computer Systems Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=65714e8b775bf6a7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dd687fff009d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OIPA Engineer</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>ML Engineer / AI Operations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
+          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plainview, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87865932a988f1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HB Mechanical Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>Software Engineer, Martech New</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HB Mechanical Group</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3155,76 +3155,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer, Martech New</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>The Knot Worldwide</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>

--- a/results/job_matches_2026-04-02.xlsx
+++ b/results/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Fullstack Developer</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5dd3623fd24e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, SQL Server, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Sr IT Engineer Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr IT Engineer Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5e69b720a3e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Microsoft Fabric)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rincon Consultants</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ventura, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cdaaeb02e957b7</t>
+          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d78630564d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb271fe420d45b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, API Gateway, Spark, PySpark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca247a6ddeb8db5</t>
+          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer - Career</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
+          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=86eda45642b35f74</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cbae5136460a7e3c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244478743fd45c43</t>
+          <t>https://www.indeed.com/viewjob?jk=cf75a697c95a13e8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476e5472ac0e7559</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
+          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Appian Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ae5008128b54d1</t>
+          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Appian Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b611b338e133dd</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Web Developer</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GameChange Solar</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software DB Development Engineer</t>
+          <t>Software Engineer - Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transaction Network Services</t>
+          <t>GameChange Solar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Oracle, DynamoDB, ETL, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SQS, IAM, YARN, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dddd28375427c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f312004f15101d48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Independent Contractor (1099) – Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Phoenix Rescue Mission</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>East Brunswick, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>PlanOmatic HQ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Java &amp; Spring Boot)</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PlanOmatic HQ</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05a0e8c331ccaeb</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Developer) -In office, Alpharetta, GA</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66615c03a2ee5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72155de26728e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Korean Bilingual Unix Adminstrator</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631ee05a50bf721</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Cloud Site Reliability Engineering</t>
+          <t>Data Architect - Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f499dac9552b99</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a7057e5ff0c30b</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56df8a42439ec061</t>
+          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Computer Systems Analyst</t>
+          <t>Engineer 2 (Full-Time) - Special Projects Department</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65714e8b775bf6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3cce96ea0c7ff3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062c4fc407951a70</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
+          <t>System Engineer (Application and Batch)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
+          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>REMOTE - Senior Software Engineer (BEDAP) Contingent</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TAXI &amp; LIMOUSINE COMMISSION</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9f61209bb4a310</t>
+          <t>https://www.indeed.com/viewjob?jk=02326ca908f92176</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, PostgreSQL, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9525a5a7c62864fb</t>
+          <t>https://www.indeed.com/viewjob?jk=98bcbec2246e7e18</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>System Engineer (Application and Batch)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Redshift, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089406942f32d443</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Senior Platform Engineer (Kafka/Flink)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Colonial Pipeline Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, ETL, MLOps, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, dbt, Power BI, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be223724b244509d</t>
+          <t>https://www.indeed.com/viewjob?jk=60336f38a0bbb5f4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b514b093e0ce21</t>
+          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sofware Engineer - 2 (Full Stack Java + Oracle Database)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Data Modeling, ETL, CI/CD, Maven</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b211924cfd00cb15</t>
+          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Kafka/Flink)</t>
+          <t>OIPA Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Marietta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569f00299d9ec3c</t>
+          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e680956ea7cc6ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Google Cloud Platform DevOps Developer 5 (contract)</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Terraform, Kubernetes, Git</t>
+          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb900ba4e1c65b40</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git, Python</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Kafka, Snowflake, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752b484810893d86</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior System Engineer / Linux Server / Server Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Astreya Partners</t>
+          <t>HB Mechanical Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29469eeada6bbae7</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,367 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601af57d4756727c</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Software Engineer II (C#) - Substantiation Platform - Hybrid</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=987d4b774583d481</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=739805211e355e27</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>OIPA Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72569a8cf3b78803</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Java Engineer (Microservices &amp; Cloud)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Centric Consulting</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4140d39a03bf0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Solutions Engineer - Data Visualization</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4be22268f3b3617e</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Zendesk</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Data Platform Developer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>HB Mechanical Group</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fefc4462aa78fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Backend Developer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3d4b0847bf4491fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer, Martech New</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>The Knot Worldwide</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
         </is>
       </c>
     </row>
